--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113241936</v>
+        <v>113242126</v>
       </c>
       <c r="B11" t="n">
-        <v>89993</v>
+        <v>91282</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,25 +1795,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600702</v>
+        <v>600639</v>
       </c>
       <c r="R11" t="n">
-        <v>6614017</v>
+        <v>6613969</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1869,11 +1869,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1894,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242126</v>
+        <v>113241936</v>
       </c>
       <c r="B12" t="n">
-        <v>91282</v>
+        <v>89993</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,25 +1901,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600639</v>
+        <v>600702</v>
       </c>
       <c r="R12" t="n">
-        <v>6613969</v>
+        <v>6614017</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1980,6 +1975,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242085</v>
+        <v>113242256</v>
       </c>
       <c r="B10" t="n">
-        <v>91300</v>
+        <v>94108</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>789</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600656</v>
+        <v>600764</v>
       </c>
       <c r="R10" t="n">
-        <v>6613968</v>
+        <v>6614027</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242126</v>
+        <v>113242234</v>
       </c>
       <c r="B11" t="n">
-        <v>91282</v>
+        <v>91306</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,25 +1795,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600639</v>
+        <v>600685</v>
       </c>
       <c r="R11" t="n">
-        <v>6613969</v>
+        <v>6613957</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113241936</v>
+        <v>113242233</v>
       </c>
       <c r="B12" t="n">
-        <v>89993</v>
+        <v>91306</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1905,21 +1905,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600702</v>
+        <v>600782</v>
       </c>
       <c r="R12" t="n">
-        <v>6614017</v>
+        <v>6613922</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,11 +1975,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2000,10 +1995,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242035</v>
+        <v>113242085</v>
       </c>
       <c r="B13" t="n">
-        <v>83743</v>
+        <v>91316</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,25 +2007,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3518</v>
+        <v>789</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2040,10 +2035,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600761</v>
+        <v>600656</v>
       </c>
       <c r="R13" t="n">
-        <v>6614032</v>
+        <v>6613968</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2109,7 +2104,7 @@
         <v>113241998</v>
       </c>
       <c r="B14" t="n">
-        <v>90029</v>
+        <v>90045</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2217,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242256</v>
+        <v>113242201</v>
       </c>
       <c r="B15" t="n">
-        <v>94092</v>
+        <v>90442</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600764</v>
+        <v>600760</v>
       </c>
       <c r="R15" t="n">
-        <v>6614027</v>
+        <v>6614099</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2323,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242234</v>
+        <v>113242126</v>
       </c>
       <c r="B16" t="n">
-        <v>91290</v>
+        <v>91298</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,25 +2330,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600685</v>
+        <v>600639</v>
       </c>
       <c r="R16" t="n">
-        <v>6613957</v>
+        <v>6613969</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242125</v>
+        <v>113242035</v>
       </c>
       <c r="B17" t="n">
-        <v>91282</v>
+        <v>83759</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,25 +2436,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>3518</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600694</v>
+        <v>600761</v>
       </c>
       <c r="R17" t="n">
-        <v>6613968</v>
+        <v>6614032</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2535,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242233</v>
+        <v>113242163</v>
       </c>
       <c r="B18" t="n">
-        <v>91290</v>
+        <v>97314</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,25 +2542,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2575,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600782</v>
+        <v>600840</v>
       </c>
       <c r="R18" t="n">
-        <v>6613922</v>
+        <v>6614040</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2641,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242163</v>
+        <v>113242125</v>
       </c>
       <c r="B19" t="n">
-        <v>97298</v>
+        <v>91298</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,25 +2648,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600840</v>
+        <v>600694</v>
       </c>
       <c r="R19" t="n">
-        <v>6614040</v>
+        <v>6613968</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2747,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242201</v>
+        <v>113241936</v>
       </c>
       <c r="B20" t="n">
-        <v>90426</v>
+        <v>90009</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,21 +2758,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5420</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,10 +2782,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600760</v>
+        <v>600702</v>
       </c>
       <c r="R20" t="n">
-        <v>6614099</v>
+        <v>6614017</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2833,6 +2828,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242256</v>
+        <v>113242126</v>
       </c>
       <c r="B10" t="n">
-        <v>94108</v>
+        <v>91298</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600764</v>
+        <v>600639</v>
       </c>
       <c r="R10" t="n">
-        <v>6614027</v>
+        <v>6613969</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242234</v>
+        <v>113241936</v>
       </c>
       <c r="B11" t="n">
-        <v>91306</v>
+        <v>90009</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600685</v>
+        <v>600702</v>
       </c>
       <c r="R11" t="n">
-        <v>6613957</v>
+        <v>6614017</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1869,6 +1869,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1889,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242233</v>
+        <v>113241998</v>
       </c>
       <c r="B12" t="n">
-        <v>91306</v>
+        <v>90045</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,25 +1906,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600782</v>
+        <v>600553</v>
       </c>
       <c r="R12" t="n">
-        <v>6613922</v>
+        <v>6614072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,6 +1980,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1995,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242085</v>
+        <v>113242163</v>
       </c>
       <c r="B13" t="n">
-        <v>91316</v>
+        <v>97314</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,25 +2017,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>789</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2035,10 +2045,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600656</v>
+        <v>600840</v>
       </c>
       <c r="R13" t="n">
-        <v>6613968</v>
+        <v>6614040</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2101,10 +2111,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113241998</v>
+        <v>113242125</v>
       </c>
       <c r="B14" t="n">
-        <v>90045</v>
+        <v>91298</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,21 +2127,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2141,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600553</v>
+        <v>600694</v>
       </c>
       <c r="R14" t="n">
-        <v>6614072</v>
+        <v>6613968</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2187,11 +2197,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2212,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242201</v>
+        <v>113242035</v>
       </c>
       <c r="B15" t="n">
-        <v>90442</v>
+        <v>83759</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,21 +2233,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>3518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600760</v>
+        <v>600761</v>
       </c>
       <c r="R15" t="n">
-        <v>6614099</v>
+        <v>6614032</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2318,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242126</v>
+        <v>113242240</v>
       </c>
       <c r="B16" t="n">
-        <v>91298</v>
+        <v>5164</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,25 +2335,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600639</v>
+        <v>600690</v>
       </c>
       <c r="R16" t="n">
-        <v>6613969</v>
+        <v>6614075</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2404,6 +2409,11 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2424,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242035</v>
+        <v>113242233</v>
       </c>
       <c r="B17" t="n">
-        <v>83759</v>
+        <v>91306</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,21 +2450,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3518</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2464,10 +2474,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600761</v>
+        <v>600782</v>
       </c>
       <c r="R17" t="n">
-        <v>6614032</v>
+        <v>6613922</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2530,10 +2540,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242163</v>
+        <v>113242201</v>
       </c>
       <c r="B18" t="n">
-        <v>97314</v>
+        <v>90442</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,25 +2552,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2570,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600840</v>
+        <v>600760</v>
       </c>
       <c r="R18" t="n">
-        <v>6614040</v>
+        <v>6614099</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2636,10 +2646,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242125</v>
+        <v>113242085</v>
       </c>
       <c r="B19" t="n">
-        <v>91298</v>
+        <v>91316</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,25 +2658,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>789</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2676,7 +2686,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600694</v>
+        <v>600656</v>
       </c>
       <c r="R19" t="n">
         <v>6613968</v>
@@ -2742,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113241936</v>
+        <v>113242256</v>
       </c>
       <c r="B20" t="n">
-        <v>90009</v>
+        <v>94108</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,21 +2768,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600702</v>
+        <v>600764</v>
       </c>
       <c r="R20" t="n">
-        <v>6614017</v>
+        <v>6614027</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2828,11 +2838,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2853,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242240</v>
+        <v>113242234</v>
       </c>
       <c r="B21" t="n">
-        <v>5164</v>
+        <v>91306</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,21 +2874,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600690</v>
+        <v>600685</v>
       </c>
       <c r="R21" t="n">
-        <v>6614075</v>
+        <v>6613957</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2939,11 +2944,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242126</v>
+        <v>113242125</v>
       </c>
       <c r="B10" t="n">
-        <v>91298</v>
+        <v>91310</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600639</v>
+        <v>600694</v>
       </c>
       <c r="R10" t="n">
-        <v>6613969</v>
+        <v>6613968</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113241936</v>
+        <v>113242256</v>
       </c>
       <c r="B11" t="n">
-        <v>90009</v>
+        <v>94120</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600702</v>
+        <v>600764</v>
       </c>
       <c r="R11" t="n">
-        <v>6614017</v>
+        <v>6614027</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1869,11 +1869,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1897,7 +1892,7 @@
         <v>113241998</v>
       </c>
       <c r="B12" t="n">
-        <v>90045</v>
+        <v>90057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2005,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242163</v>
+        <v>113242234</v>
       </c>
       <c r="B13" t="n">
-        <v>97314</v>
+        <v>91318</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,25 +2012,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2045,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600840</v>
+        <v>600685</v>
       </c>
       <c r="R13" t="n">
-        <v>6614040</v>
+        <v>6613957</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2111,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113242125</v>
+        <v>113242163</v>
       </c>
       <c r="B14" t="n">
-        <v>91298</v>
+        <v>97326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,25 +2118,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600694</v>
+        <v>600840</v>
       </c>
       <c r="R14" t="n">
-        <v>6613968</v>
+        <v>6614040</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2217,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242035</v>
+        <v>113242126</v>
       </c>
       <c r="B15" t="n">
-        <v>83759</v>
+        <v>91310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,25 +2224,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3518</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600761</v>
+        <v>600639</v>
       </c>
       <c r="R15" t="n">
-        <v>6614032</v>
+        <v>6613969</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2323,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242240</v>
+        <v>113241936</v>
       </c>
       <c r="B16" t="n">
-        <v>5164</v>
+        <v>90021</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2339,21 +2334,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600690</v>
+        <v>600702</v>
       </c>
       <c r="R16" t="n">
-        <v>6614075</v>
+        <v>6614017</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2412,7 +2407,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2434,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242233</v>
+        <v>113242201</v>
       </c>
       <c r="B17" t="n">
-        <v>91306</v>
+        <v>90454</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2450,21 +2445,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600782</v>
+        <v>600760</v>
       </c>
       <c r="R17" t="n">
-        <v>6613922</v>
+        <v>6614099</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2540,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242201</v>
+        <v>113242085</v>
       </c>
       <c r="B18" t="n">
-        <v>90442</v>
+        <v>91328</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2552,25 +2547,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>789</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600760</v>
+        <v>600656</v>
       </c>
       <c r="R18" t="n">
-        <v>6614099</v>
+        <v>6613968</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2646,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242085</v>
+        <v>113242233</v>
       </c>
       <c r="B19" t="n">
-        <v>91316</v>
+        <v>91318</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,25 +2653,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>789</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2686,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600656</v>
+        <v>600782</v>
       </c>
       <c r="R19" t="n">
-        <v>6613968</v>
+        <v>6613922</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242256</v>
+        <v>113242035</v>
       </c>
       <c r="B20" t="n">
-        <v>94108</v>
+        <v>83771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,21 +2763,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2180</v>
+        <v>3518</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600764</v>
+        <v>600761</v>
       </c>
       <c r="R20" t="n">
-        <v>6614027</v>
+        <v>6614032</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2858,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242234</v>
+        <v>113242240</v>
       </c>
       <c r="B21" t="n">
-        <v>91306</v>
+        <v>5164</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,21 +2869,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2893,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600685</v>
+        <v>600690</v>
       </c>
       <c r="R21" t="n">
-        <v>6613957</v>
+        <v>6614075</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2944,6 +2939,11 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,7 +1677,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242125</v>
+        <v>113242126</v>
       </c>
       <c r="B10" t="n">
         <v>91310</v>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600694</v>
+        <v>600639</v>
       </c>
       <c r="R10" t="n">
-        <v>6613968</v>
+        <v>6613969</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242256</v>
+        <v>113242035</v>
       </c>
       <c r="B11" t="n">
-        <v>94120</v>
+        <v>83771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>3518</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600764</v>
+        <v>600761</v>
       </c>
       <c r="R11" t="n">
-        <v>6614027</v>
+        <v>6614032</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1889,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113241998</v>
+        <v>113242256</v>
       </c>
       <c r="B12" t="n">
-        <v>90057</v>
+        <v>94120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,25 +1901,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600553</v>
+        <v>600764</v>
       </c>
       <c r="R12" t="n">
-        <v>6614072</v>
+        <v>6614027</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,11 +1975,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2106,10 +2101,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113242163</v>
+        <v>113241936</v>
       </c>
       <c r="B14" t="n">
-        <v>97326</v>
+        <v>90021</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,25 +2113,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2146,10 +2141,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600840</v>
+        <v>600702</v>
       </c>
       <c r="R14" t="n">
-        <v>6614040</v>
+        <v>6614017</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2192,6 +2187,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2212,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242126</v>
+        <v>113242201</v>
       </c>
       <c r="B15" t="n">
-        <v>91310</v>
+        <v>90454</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,25 +2224,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600639</v>
+        <v>600760</v>
       </c>
       <c r="R15" t="n">
-        <v>6613969</v>
+        <v>6614099</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2318,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113241936</v>
+        <v>113242233</v>
       </c>
       <c r="B16" t="n">
-        <v>90021</v>
+        <v>91318</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,21 +2334,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600702</v>
+        <v>600782</v>
       </c>
       <c r="R16" t="n">
-        <v>6614017</v>
+        <v>6613922</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2404,11 +2404,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2429,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242201</v>
+        <v>113241998</v>
       </c>
       <c r="B17" t="n">
-        <v>90454</v>
+        <v>90057</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,25 +2436,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600760</v>
+        <v>600553</v>
       </c>
       <c r="R17" t="n">
-        <v>6614099</v>
+        <v>6614072</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2515,6 +2510,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2535,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242085</v>
+        <v>113242125</v>
       </c>
       <c r="B18" t="n">
-        <v>91328</v>
+        <v>91310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,25 +2547,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>789</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600656</v>
+        <v>600694</v>
       </c>
       <c r="R18" t="n">
         <v>6613968</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242233</v>
+        <v>113242240</v>
       </c>
       <c r="B19" t="n">
-        <v>91318</v>
+        <v>5164</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,21 +2657,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600782</v>
+        <v>600690</v>
       </c>
       <c r="R19" t="n">
-        <v>6613922</v>
+        <v>6614075</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2727,6 +2727,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2747,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242035</v>
+        <v>113242085</v>
       </c>
       <c r="B20" t="n">
-        <v>83771</v>
+        <v>91328</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,25 +2764,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3518</v>
+        <v>789</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600761</v>
+        <v>600656</v>
       </c>
       <c r="R20" t="n">
-        <v>6614032</v>
+        <v>6613968</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2853,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242240</v>
+        <v>113242163</v>
       </c>
       <c r="B21" t="n">
-        <v>5164</v>
+        <v>97326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,25 +2870,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600690</v>
+        <v>600840</v>
       </c>
       <c r="R21" t="n">
-        <v>6614075</v>
+        <v>6614040</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2939,11 +2944,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242126</v>
+        <v>113242035</v>
       </c>
       <c r="B10" t="n">
-        <v>91310</v>
+        <v>83771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1689,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>3518</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600639</v>
+        <v>600761</v>
       </c>
       <c r="R10" t="n">
-        <v>6613969</v>
+        <v>6614032</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242035</v>
+        <v>113242126</v>
       </c>
       <c r="B11" t="n">
-        <v>83771</v>
+        <v>91310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,25 +1795,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3518</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600761</v>
+        <v>600639</v>
       </c>
       <c r="R11" t="n">
-        <v>6614032</v>
+        <v>6613969</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242240</v>
+        <v>113242085</v>
       </c>
       <c r="B19" t="n">
-        <v>5164</v>
+        <v>91328</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,25 +2653,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>789</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600690</v>
+        <v>600656</v>
       </c>
       <c r="R19" t="n">
-        <v>6614075</v>
+        <v>6613968</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2727,11 +2727,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2752,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242085</v>
+        <v>113242240</v>
       </c>
       <c r="B20" t="n">
-        <v>91328</v>
+        <v>5164</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2764,25 +2759,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>789</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600656</v>
+        <v>600690</v>
       </c>
       <c r="R20" t="n">
-        <v>6613968</v>
+        <v>6614075</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2838,6 +2833,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242035</v>
+        <v>113242240</v>
       </c>
       <c r="B10" t="n">
-        <v>83771</v>
+        <v>5164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3518</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600761</v>
+        <v>600690</v>
       </c>
       <c r="R10" t="n">
-        <v>6614032</v>
+        <v>6614075</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1763,6 +1763,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1783,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242126</v>
+        <v>113242163</v>
       </c>
       <c r="B11" t="n">
-        <v>91310</v>
+        <v>97348</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,25 +1800,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1828,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600639</v>
+        <v>600840</v>
       </c>
       <c r="R11" t="n">
-        <v>6613969</v>
+        <v>6614040</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1889,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242256</v>
+        <v>113242234</v>
       </c>
       <c r="B12" t="n">
-        <v>94120</v>
+        <v>91340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1905,21 +1910,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600764</v>
+        <v>600685</v>
       </c>
       <c r="R12" t="n">
-        <v>6614027</v>
+        <v>6613957</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1995,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242234</v>
+        <v>113242201</v>
       </c>
       <c r="B13" t="n">
-        <v>91318</v>
+        <v>90476</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2011,21 +2016,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2035,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600685</v>
+        <v>600760</v>
       </c>
       <c r="R13" t="n">
-        <v>6613957</v>
+        <v>6614099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2104,7 +2109,7 @@
         <v>113241936</v>
       </c>
       <c r="B14" t="n">
-        <v>90021</v>
+        <v>90043</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2212,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242201</v>
+        <v>113242256</v>
       </c>
       <c r="B15" t="n">
-        <v>90454</v>
+        <v>94142</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,21 +2233,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600760</v>
+        <v>600764</v>
       </c>
       <c r="R15" t="n">
-        <v>6614099</v>
+        <v>6614027</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2318,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242233</v>
+        <v>113242125</v>
       </c>
       <c r="B16" t="n">
-        <v>91318</v>
+        <v>91332</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,25 +2335,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600782</v>
+        <v>600694</v>
       </c>
       <c r="R16" t="n">
-        <v>6613922</v>
+        <v>6613968</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113241998</v>
+        <v>113242085</v>
       </c>
       <c r="B17" t="n">
-        <v>90057</v>
+        <v>91350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,25 +2441,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>789</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600553</v>
+        <v>600656</v>
       </c>
       <c r="R17" t="n">
-        <v>6614072</v>
+        <v>6613968</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2510,11 +2515,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2535,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242125</v>
+        <v>113242233</v>
       </c>
       <c r="B18" t="n">
-        <v>91310</v>
+        <v>91340</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,25 +2547,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600694</v>
+        <v>600782</v>
       </c>
       <c r="R18" t="n">
-        <v>6613968</v>
+        <v>6613922</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242085</v>
+        <v>113242126</v>
       </c>
       <c r="B19" t="n">
-        <v>91328</v>
+        <v>91332</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,25 +2653,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>789</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600656</v>
+        <v>600639</v>
       </c>
       <c r="R19" t="n">
-        <v>6613968</v>
+        <v>6613969</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242240</v>
+        <v>113242035</v>
       </c>
       <c r="B20" t="n">
-        <v>5164</v>
+        <v>83793</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,21 +2763,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>3518</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600690</v>
+        <v>600761</v>
       </c>
       <c r="R20" t="n">
-        <v>6614075</v>
+        <v>6614032</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2833,11 +2833,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2858,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242163</v>
+        <v>113241998</v>
       </c>
       <c r="B21" t="n">
-        <v>97326</v>
+        <v>90079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,25 +2865,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2893,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600840</v>
+        <v>600553</v>
       </c>
       <c r="R21" t="n">
-        <v>6614040</v>
+        <v>6614072</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2945,6 +2940,11 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -2959,6 +2959,262 @@
       <c r="AY21" t="inlineStr">
         <is>
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113532143</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97348</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>600840</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6613984</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>U-Väs-1487</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe, Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113532120</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97348</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>600749</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6613972</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>U-Väs-1486</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe, Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242240</v>
+        <v>113242256</v>
       </c>
       <c r="B10" t="n">
-        <v>5164</v>
+        <v>94146</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600690</v>
+        <v>600764</v>
       </c>
       <c r="R10" t="n">
-        <v>6614075</v>
+        <v>6614027</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1763,11 +1763,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1788,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242163</v>
+        <v>113242234</v>
       </c>
       <c r="B11" t="n">
-        <v>97348</v>
+        <v>91344</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,25 +1795,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1828,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600840</v>
+        <v>600685</v>
       </c>
       <c r="R11" t="n">
-        <v>6614040</v>
+        <v>6613957</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1894,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242234</v>
+        <v>113241998</v>
       </c>
       <c r="B12" t="n">
-        <v>91340</v>
+        <v>90083</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,25 +1901,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600685</v>
+        <v>600553</v>
       </c>
       <c r="R12" t="n">
-        <v>6613957</v>
+        <v>6614072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1980,6 +1975,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2003,7 +2003,7 @@
         <v>113242201</v>
       </c>
       <c r="B13" t="n">
-        <v>90476</v>
+        <v>90480</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113241936</v>
+        <v>113242233</v>
       </c>
       <c r="B14" t="n">
-        <v>90043</v>
+        <v>91344</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2122,21 +2122,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600702</v>
+        <v>600782</v>
       </c>
       <c r="R14" t="n">
-        <v>6614017</v>
+        <v>6613922</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2192,11 +2192,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2217,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242256</v>
+        <v>113242035</v>
       </c>
       <c r="B15" t="n">
-        <v>94142</v>
+        <v>83797</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>3518</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600764</v>
+        <v>600761</v>
       </c>
       <c r="R15" t="n">
-        <v>6614027</v>
+        <v>6614032</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2323,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242125</v>
+        <v>113242085</v>
       </c>
       <c r="B16" t="n">
-        <v>91332</v>
+        <v>91354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,25 +2330,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>789</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,7 +2358,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600694</v>
+        <v>600656</v>
       </c>
       <c r="R16" t="n">
         <v>6613968</v>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242085</v>
+        <v>113242125</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,25 +2436,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>789</v>
+        <v>4361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2469,7 +2464,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600656</v>
+        <v>600694</v>
       </c>
       <c r="R17" t="n">
         <v>6613968</v>
@@ -2535,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242233</v>
+        <v>113241936</v>
       </c>
       <c r="B18" t="n">
-        <v>91340</v>
+        <v>90047</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2551,21 +2546,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2575,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600782</v>
+        <v>600702</v>
       </c>
       <c r="R18" t="n">
-        <v>6613922</v>
+        <v>6614017</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,6 +2616,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2641,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242126</v>
+        <v>113242163</v>
       </c>
       <c r="B19" t="n">
-        <v>91332</v>
+        <v>97352</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,25 +2653,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600639</v>
+        <v>600840</v>
       </c>
       <c r="R19" t="n">
-        <v>6613969</v>
+        <v>6614040</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242035</v>
+        <v>113242126</v>
       </c>
       <c r="B20" t="n">
-        <v>83793</v>
+        <v>91336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,25 +2759,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3518</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600761</v>
+        <v>600639</v>
       </c>
       <c r="R20" t="n">
-        <v>6614032</v>
+        <v>6613969</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113241998</v>
+        <v>113242240</v>
       </c>
       <c r="B21" t="n">
-        <v>90079</v>
+        <v>5164</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,25 +2865,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600553</v>
+        <v>600690</v>
       </c>
       <c r="R21" t="n">
-        <v>6614072</v>
+        <v>6614075</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>granved</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113532143</v>
+        <v>113532120</v>
       </c>
       <c r="B22" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3016,14 +3016,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600840</v>
+        <v>600749</v>
       </c>
       <c r="R22" t="n">
-        <v>6613984</v>
+        <v>6613972</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>U-Väs-1487</t>
+          <t>U-Väs-1486</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3092,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113532120</v>
+        <v>113532143</v>
       </c>
       <c r="B23" t="n">
-        <v>97348</v>
+        <v>97352</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3144,14 +3144,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600749</v>
+        <v>600840</v>
       </c>
       <c r="R23" t="n">
-        <v>6613972</v>
+        <v>6613984</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>U-Väs-1486</t>
+          <t>U-Väs-1487</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242256</v>
+        <v>113242035</v>
       </c>
       <c r="B10" t="n">
-        <v>94146</v>
+        <v>83797</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>3518</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600764</v>
+        <v>600761</v>
       </c>
       <c r="R10" t="n">
-        <v>6614027</v>
+        <v>6614032</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1783,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242234</v>
+        <v>113241998</v>
       </c>
       <c r="B11" t="n">
-        <v>91344</v>
+        <v>90083</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,25 +1795,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600685</v>
+        <v>600553</v>
       </c>
       <c r="R11" t="n">
-        <v>6613957</v>
+        <v>6614072</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1869,6 +1869,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1889,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113241998</v>
+        <v>113242085</v>
       </c>
       <c r="B12" t="n">
-        <v>90083</v>
+        <v>91354</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,25 +1906,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>789</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600553</v>
+        <v>600656</v>
       </c>
       <c r="R12" t="n">
-        <v>6614072</v>
+        <v>6613968</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,11 +1980,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2000,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242201</v>
+        <v>113242256</v>
       </c>
       <c r="B13" t="n">
-        <v>90480</v>
+        <v>94146</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600760</v>
+        <v>600764</v>
       </c>
       <c r="R13" t="n">
-        <v>6614099</v>
+        <v>6614027</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113242233</v>
+        <v>113242163</v>
       </c>
       <c r="B14" t="n">
-        <v>91344</v>
+        <v>97352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,25 +2118,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600782</v>
+        <v>600840</v>
       </c>
       <c r="R14" t="n">
-        <v>6613922</v>
+        <v>6614040</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242035</v>
+        <v>113241936</v>
       </c>
       <c r="B15" t="n">
-        <v>83797</v>
+        <v>90047</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3518</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600761</v>
+        <v>600702</v>
       </c>
       <c r="R15" t="n">
-        <v>6614032</v>
+        <v>6614017</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2298,6 +2298,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2318,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242085</v>
+        <v>113242126</v>
       </c>
       <c r="B16" t="n">
-        <v>91354</v>
+        <v>91336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,25 +2335,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>789</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600656</v>
+        <v>600639</v>
       </c>
       <c r="R16" t="n">
-        <v>6613968</v>
+        <v>6613969</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2530,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113241936</v>
+        <v>113242201</v>
       </c>
       <c r="B18" t="n">
-        <v>90047</v>
+        <v>90480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,21 +2551,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>5420</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2570,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600702</v>
+        <v>600760</v>
       </c>
       <c r="R18" t="n">
-        <v>6614017</v>
+        <v>6614099</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2616,11 +2621,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2641,10 +2641,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242163</v>
+        <v>113242233</v>
       </c>
       <c r="B19" t="n">
-        <v>97352</v>
+        <v>91344</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,25 +2653,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600840</v>
+        <v>600782</v>
       </c>
       <c r="R19" t="n">
-        <v>6614040</v>
+        <v>6613922</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2747,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242126</v>
+        <v>113242240</v>
       </c>
       <c r="B20" t="n">
-        <v>91336</v>
+        <v>5164</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,25 +2759,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600639</v>
+        <v>600690</v>
       </c>
       <c r="R20" t="n">
-        <v>6613969</v>
+        <v>6614075</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2833,6 +2833,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2853,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242240</v>
+        <v>113242234</v>
       </c>
       <c r="B21" t="n">
-        <v>5164</v>
+        <v>91344</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2869,21 +2874,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600690</v>
+        <v>600685</v>
       </c>
       <c r="R21" t="n">
-        <v>6614075</v>
+        <v>6613957</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2939,11 +2944,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242035</v>
+        <v>113241936</v>
       </c>
       <c r="B10" t="n">
-        <v>83797</v>
+        <v>90053</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3518</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600761</v>
+        <v>600702</v>
       </c>
       <c r="R10" t="n">
-        <v>6614032</v>
+        <v>6614017</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1763,6 +1763,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1783,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113241998</v>
+        <v>113242085</v>
       </c>
       <c r="B11" t="n">
-        <v>90083</v>
+        <v>91360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,25 +1800,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>789</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1828,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600553</v>
+        <v>600656</v>
       </c>
       <c r="R11" t="n">
-        <v>6614072</v>
+        <v>6613968</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1869,11 +1874,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1894,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242085</v>
+        <v>113242233</v>
       </c>
       <c r="B12" t="n">
-        <v>91354</v>
+        <v>91350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,25 +1906,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>789</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600656</v>
+        <v>600782</v>
       </c>
       <c r="R12" t="n">
-        <v>6613968</v>
+        <v>6613922</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242256</v>
+        <v>113242201</v>
       </c>
       <c r="B13" t="n">
-        <v>94146</v>
+        <v>90486</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600764</v>
+        <v>600760</v>
       </c>
       <c r="R13" t="n">
-        <v>6614027</v>
+        <v>6614099</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113242163</v>
+        <v>113242234</v>
       </c>
       <c r="B14" t="n">
-        <v>97352</v>
+        <v>91350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2118,25 +2118,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600840</v>
+        <v>600685</v>
       </c>
       <c r="R14" t="n">
-        <v>6614040</v>
+        <v>6613957</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2212,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113241936</v>
+        <v>113242125</v>
       </c>
       <c r="B15" t="n">
-        <v>90047</v>
+        <v>91342</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,25 +2224,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>4361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600702</v>
+        <v>600694</v>
       </c>
       <c r="R15" t="n">
-        <v>6614017</v>
+        <v>6613968</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2298,11 +2298,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2323,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242126</v>
+        <v>113242163</v>
       </c>
       <c r="B16" t="n">
-        <v>91336</v>
+        <v>97358</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2335,25 +2330,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600639</v>
+        <v>600840</v>
       </c>
       <c r="R16" t="n">
-        <v>6613969</v>
+        <v>6614040</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242125</v>
+        <v>113242126</v>
       </c>
       <c r="B17" t="n">
-        <v>91336</v>
+        <v>91342</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600694</v>
+        <v>600639</v>
       </c>
       <c r="R17" t="n">
-        <v>6613968</v>
+        <v>6613969</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2535,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242201</v>
+        <v>113242035</v>
       </c>
       <c r="B18" t="n">
-        <v>90480</v>
+        <v>83803</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2551,21 +2546,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5420</v>
+        <v>3518</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2575,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600760</v>
+        <v>600761</v>
       </c>
       <c r="R18" t="n">
-        <v>6614099</v>
+        <v>6614032</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2641,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242233</v>
+        <v>113241998</v>
       </c>
       <c r="B19" t="n">
-        <v>91344</v>
+        <v>90089</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,25 +2648,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600782</v>
+        <v>600553</v>
       </c>
       <c r="R19" t="n">
-        <v>6613922</v>
+        <v>6614072</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2727,6 +2722,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242234</v>
+        <v>113242256</v>
       </c>
       <c r="B21" t="n">
-        <v>91344</v>
+        <v>94152</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,21 +2874,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600685</v>
+        <v>600764</v>
       </c>
       <c r="R21" t="n">
-        <v>6613957</v>
+        <v>6614027</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113532120</v>
+        <v>113532143</v>
       </c>
       <c r="B22" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3016,14 +3016,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600749</v>
+        <v>600840</v>
       </c>
       <c r="R22" t="n">
-        <v>6613972</v>
+        <v>6613984</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>U-Väs-1486</t>
+          <t>U-Väs-1487</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3092,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113532143</v>
+        <v>113532120</v>
       </c>
       <c r="B23" t="n">
-        <v>97352</v>
+        <v>97358</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3144,14 +3144,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600840</v>
+        <v>600749</v>
       </c>
       <c r="R23" t="n">
-        <v>6613984</v>
+        <v>6613972</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>U-Väs-1487</t>
+          <t>U-Väs-1486</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113241936</v>
+        <v>113242233</v>
       </c>
       <c r="B10" t="n">
-        <v>90053</v>
+        <v>91350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600702</v>
+        <v>600782</v>
       </c>
       <c r="R10" t="n">
-        <v>6614017</v>
+        <v>6613922</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1763,11 +1763,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1788,10 +1783,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242085</v>
+        <v>113242240</v>
       </c>
       <c r="B11" t="n">
-        <v>91360</v>
+        <v>5164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,25 +1795,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>789</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1828,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600656</v>
+        <v>600690</v>
       </c>
       <c r="R11" t="n">
-        <v>6613968</v>
+        <v>6614075</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1874,6 +1869,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1894,7 +1894,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242233</v>
+        <v>113242234</v>
       </c>
       <c r="B12" t="n">
         <v>91350</v>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600782</v>
+        <v>600685</v>
       </c>
       <c r="R12" t="n">
-        <v>6613922</v>
+        <v>6613957</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242201</v>
+        <v>113241936</v>
       </c>
       <c r="B13" t="n">
-        <v>90486</v>
+        <v>90053</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2016,21 +2016,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600760</v>
+        <v>600702</v>
       </c>
       <c r="R13" t="n">
-        <v>6614099</v>
+        <v>6614017</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2086,6 +2086,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2106,10 +2111,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113242234</v>
+        <v>113242035</v>
       </c>
       <c r="B14" t="n">
-        <v>91350</v>
+        <v>83803</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2122,21 +2127,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>3518</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2146,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600685</v>
+        <v>600761</v>
       </c>
       <c r="R14" t="n">
-        <v>6613957</v>
+        <v>6614032</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2212,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242125</v>
+        <v>113242256</v>
       </c>
       <c r="B15" t="n">
-        <v>91342</v>
+        <v>94152</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2224,25 +2229,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600694</v>
+        <v>600764</v>
       </c>
       <c r="R15" t="n">
-        <v>6613968</v>
+        <v>6614027</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2318,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242163</v>
+        <v>113242201</v>
       </c>
       <c r="B16" t="n">
-        <v>97358</v>
+        <v>90486</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,25 +2335,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600840</v>
+        <v>600760</v>
       </c>
       <c r="R16" t="n">
-        <v>6614040</v>
+        <v>6614099</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2424,10 +2429,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242126</v>
+        <v>113242085</v>
       </c>
       <c r="B17" t="n">
-        <v>91342</v>
+        <v>91360</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2436,25 +2441,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>789</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600639</v>
+        <v>600656</v>
       </c>
       <c r="R17" t="n">
-        <v>6613969</v>
+        <v>6613968</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2530,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242035</v>
+        <v>113241998</v>
       </c>
       <c r="B18" t="n">
-        <v>83803</v>
+        <v>90089</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,25 +2547,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3518</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2570,10 +2575,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600761</v>
+        <v>600553</v>
       </c>
       <c r="R18" t="n">
-        <v>6614032</v>
+        <v>6614072</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2616,6 +2621,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2636,10 +2646,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113241998</v>
+        <v>113242163</v>
       </c>
       <c r="B19" t="n">
-        <v>90089</v>
+        <v>97358</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2648,25 +2658,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2676,10 +2686,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600553</v>
+        <v>600840</v>
       </c>
       <c r="R19" t="n">
-        <v>6614072</v>
+        <v>6614040</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2722,11 +2732,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2747,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242240</v>
+        <v>113242125</v>
       </c>
       <c r="B20" t="n">
-        <v>5164</v>
+        <v>91342</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2759,25 +2764,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600690</v>
+        <v>600694</v>
       </c>
       <c r="R20" t="n">
-        <v>6614075</v>
+        <v>6613968</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2833,11 +2838,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242256</v>
+        <v>113242126</v>
       </c>
       <c r="B21" t="n">
-        <v>94152</v>
+        <v>91342</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,25 +2870,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600764</v>
+        <v>600639</v>
       </c>
       <c r="R21" t="n">
-        <v>6614027</v>
+        <v>6613969</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1894,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242234</v>
+        <v>113241936</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>90053</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600685</v>
+        <v>600702</v>
       </c>
       <c r="R12" t="n">
-        <v>6613957</v>
+        <v>6614017</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1980,6 +1980,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2000,10 +2005,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113241936</v>
+        <v>113242234</v>
       </c>
       <c r="B13" t="n">
-        <v>90053</v>
+        <v>91350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2016,21 +2021,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2040,10 +2045,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600702</v>
+        <v>600685</v>
       </c>
       <c r="R13" t="n">
-        <v>6614017</v>
+        <v>6613957</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2086,11 +2091,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242256</v>
+        <v>113242201</v>
       </c>
       <c r="B15" t="n">
-        <v>94152</v>
+        <v>90486</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,21 +2233,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600764</v>
+        <v>600760</v>
       </c>
       <c r="R15" t="n">
-        <v>6614027</v>
+        <v>6614099</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2323,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242201</v>
+        <v>113242256</v>
       </c>
       <c r="B16" t="n">
-        <v>90486</v>
+        <v>94152</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600760</v>
+        <v>600764</v>
       </c>
       <c r="R16" t="n">
-        <v>6614099</v>
+        <v>6614027</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1677,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242233</v>
+        <v>113242240</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>5164</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600782</v>
+        <v>600690</v>
       </c>
       <c r="R10" t="n">
-        <v>6613922</v>
+        <v>6614075</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1763,6 +1763,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1783,10 +1788,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242240</v>
+        <v>113242125</v>
       </c>
       <c r="B11" t="n">
-        <v>5164</v>
+        <v>91349</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,25 +1800,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1823,10 +1828,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600690</v>
+        <v>600694</v>
       </c>
       <c r="R11" t="n">
-        <v>6614075</v>
+        <v>6613968</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1869,11 +1874,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1894,10 +1894,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113241936</v>
+        <v>113242035</v>
       </c>
       <c r="B12" t="n">
-        <v>90053</v>
+        <v>83810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,21 +1910,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>3518</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1934,10 +1934,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600702</v>
+        <v>600761</v>
       </c>
       <c r="R12" t="n">
-        <v>6614017</v>
+        <v>6614032</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1980,11 +1980,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2005,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242234</v>
+        <v>113242085</v>
       </c>
       <c r="B13" t="n">
-        <v>91350</v>
+        <v>91367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,25 +2012,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>789</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2045,10 +2040,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600685</v>
+        <v>600656</v>
       </c>
       <c r="R13" t="n">
-        <v>6613957</v>
+        <v>6613968</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2111,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113242035</v>
+        <v>113242201</v>
       </c>
       <c r="B14" t="n">
-        <v>83803</v>
+        <v>90493</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2127,21 +2122,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3518</v>
+        <v>5420</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2151,10 +2146,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600761</v>
+        <v>600760</v>
       </c>
       <c r="R14" t="n">
-        <v>6614032</v>
+        <v>6614099</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2217,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242201</v>
+        <v>113242233</v>
       </c>
       <c r="B15" t="n">
-        <v>90486</v>
+        <v>91357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2257,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600760</v>
+        <v>600782</v>
       </c>
       <c r="R15" t="n">
-        <v>6614099</v>
+        <v>6613922</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2326,7 +2321,7 @@
         <v>113242256</v>
       </c>
       <c r="B16" t="n">
-        <v>94152</v>
+        <v>94159</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2429,10 +2424,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242085</v>
+        <v>113242234</v>
       </c>
       <c r="B17" t="n">
-        <v>91360</v>
+        <v>91357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,25 +2436,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>789</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600656</v>
+        <v>600685</v>
       </c>
       <c r="R17" t="n">
-        <v>6613968</v>
+        <v>6613957</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2535,10 +2530,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113241998</v>
+        <v>113242126</v>
       </c>
       <c r="B18" t="n">
-        <v>90089</v>
+        <v>91349</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2551,21 +2546,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2575,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600553</v>
+        <v>600639</v>
       </c>
       <c r="R18" t="n">
-        <v>6614072</v>
+        <v>6613969</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,11 +2616,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2646,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113242163</v>
+        <v>113241998</v>
       </c>
       <c r="B19" t="n">
-        <v>97358</v>
+        <v>90096</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,25 +2648,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2686,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600840</v>
+        <v>600553</v>
       </c>
       <c r="R19" t="n">
-        <v>6614040</v>
+        <v>6614072</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2732,6 +2722,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2752,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242125</v>
+        <v>113241936</v>
       </c>
       <c r="B20" t="n">
-        <v>91342</v>
+        <v>90060</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2764,25 +2759,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2792,10 +2787,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600694</v>
+        <v>600702</v>
       </c>
       <c r="R20" t="n">
-        <v>6613968</v>
+        <v>6614017</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2838,6 +2833,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2858,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242126</v>
+        <v>113242163</v>
       </c>
       <c r="B21" t="n">
-        <v>91342</v>
+        <v>97365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,25 +2870,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600639</v>
+        <v>600840</v>
       </c>
       <c r="R21" t="n">
-        <v>6613969</v>
+        <v>6614040</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113532143</v>
+        <v>113532120</v>
       </c>
       <c r="B22" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3016,14 +3016,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600840</v>
+        <v>600749</v>
       </c>
       <c r="R22" t="n">
-        <v>6613984</v>
+        <v>6613972</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>U-Väs-1487</t>
+          <t>U-Väs-1486</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3092,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113532120</v>
+        <v>113532143</v>
       </c>
       <c r="B23" t="n">
-        <v>97358</v>
+        <v>97365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3144,14 +3144,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600749</v>
+        <v>600840</v>
       </c>
       <c r="R23" t="n">
-        <v>6613972</v>
+        <v>6613984</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>U-Väs-1486</t>
+          <t>U-Väs-1487</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2967,7 +2967,7 @@
         <v>113532120</v>
       </c>
       <c r="B22" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>113532143</v>
       </c>
       <c r="B23" t="n">
-        <v>97365</v>
+        <v>97370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113532120</v>
+        <v>113532143</v>
       </c>
       <c r="B22" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3016,14 +3016,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600749</v>
+        <v>600840</v>
       </c>
       <c r="R22" t="n">
-        <v>6613972</v>
+        <v>6613984</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>U-Väs-1486</t>
+          <t>U-Väs-1487</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3092,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113532143</v>
+        <v>113532120</v>
       </c>
       <c r="B23" t="n">
-        <v>97370</v>
+        <v>97398</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3144,14 +3144,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600840</v>
+        <v>600749</v>
       </c>
       <c r="R23" t="n">
-        <v>6613984</v>
+        <v>6613972</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>U-Väs-1487</t>
+          <t>U-Väs-1486</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113532143</v>
+        <v>113532120</v>
       </c>
       <c r="B22" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3016,14 +3016,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600840</v>
+        <v>600749</v>
       </c>
       <c r="R22" t="n">
-        <v>6613984</v>
+        <v>6613972</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>U-Väs-1487</t>
+          <t>U-Väs-1486</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3092,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113532120</v>
+        <v>113532143</v>
       </c>
       <c r="B23" t="n">
-        <v>97398</v>
+        <v>97402</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3144,14 +3144,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600749</v>
+        <v>600840</v>
       </c>
       <c r="R23" t="n">
-        <v>6613972</v>
+        <v>6613984</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>U-Väs-1486</t>
+          <t>U-Väs-1487</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2964,7 +2964,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113532120</v>
+        <v>113532143</v>
       </c>
       <c r="B22" t="n">
         <v>97402</v>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3016,14 +3016,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600749</v>
+        <v>600840</v>
       </c>
       <c r="R22" t="n">
-        <v>6613972</v>
+        <v>6613984</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>U-Väs-1486</t>
+          <t>U-Väs-1487</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3092,7 +3092,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113532143</v>
+        <v>113532120</v>
       </c>
       <c r="B23" t="n">
         <v>97402</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3144,14 +3144,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600840</v>
+        <v>600749</v>
       </c>
       <c r="R23" t="n">
-        <v>6613984</v>
+        <v>6613972</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>U-Väs-1487</t>
+          <t>U-Väs-1486</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3218,6 +3218,828 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120344691</v>
+      </c>
+      <c r="B24" t="n">
+        <v>94704</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skansen, Skansen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>600748</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6614035</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120344481</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skansen, Skansen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>600773</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6614013</v>
+      </c>
+      <c r="S25" t="n">
+        <v>12</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120344208</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>S Frögärde, S Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>600749</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6613964</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120344382</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>S Frögärde, S Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>600771</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6613982</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120343407</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>S Frögärde, S Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>600652</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6613987</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120342905</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90600</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>S Frögärde, S Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600559</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6614068</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120345023</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91272</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>S Frögärde, S Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>600529</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6614077</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3220,10 +3220,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120344691</v>
+        <v>120344208</v>
       </c>
       <c r="B24" t="n">
-        <v>94704</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3236,46 +3236,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600748</v>
+        <v>600749</v>
       </c>
       <c r="R24" t="n">
-        <v>6614035</v>
+        <v>6613964</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3304,7 +3295,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3314,7 +3305,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3341,7 +3332,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120344481</v>
+        <v>120344382</v>
       </c>
       <c r="B25" t="n">
         <v>90600</v>
@@ -3377,17 +3368,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600773</v>
+        <v>600771</v>
       </c>
       <c r="R25" t="n">
-        <v>6614013</v>
+        <v>6613982</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3416,7 +3407,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3426,7 +3417,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,10 +3444,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120344208</v>
+        <v>120344481</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3465,41 +3456,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600749</v>
+        <v>600773</v>
       </c>
       <c r="R26" t="n">
-        <v>6613964</v>
+        <v>6614013</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3528,7 +3519,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3538,7 +3529,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,10 +3556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120344382</v>
+        <v>120345023</v>
       </c>
       <c r="B27" t="n">
-        <v>90600</v>
+        <v>91272</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3577,25 +3568,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3605,13 +3596,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600771</v>
+        <v>600529</v>
       </c>
       <c r="R27" t="n">
-        <v>6613982</v>
+        <v>6614077</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3640,7 +3631,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3641,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,6 +3652,16 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3920,14 +3921,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120345023</v>
+        <v>120344691</v>
       </c>
       <c r="B30" t="n">
-        <v>91272</v>
+        <v>94704</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3936,37 +3937,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>2180</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600529</v>
+        <v>600748</v>
       </c>
       <c r="R30" t="n">
-        <v>6614077</v>
+        <v>6614035</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3995,7 +4005,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4005,7 +4015,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4016,16 +4026,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3220,10 +3220,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120344208</v>
+        <v>120345023</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>91272</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3236,21 +3236,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3260,10 +3260,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600749</v>
+        <v>600529</v>
       </c>
       <c r="R24" t="n">
-        <v>6613964</v>
+        <v>6614077</v>
       </c>
       <c r="S24" t="n">
         <v>6</v>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,6 +3316,16 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3444,7 +3454,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120344481</v>
+        <v>120342905</v>
       </c>
       <c r="B26" t="n">
         <v>90600</v>
@@ -3477,20 +3487,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600773</v>
+        <v>600559</v>
       </c>
       <c r="R26" t="n">
-        <v>6614013</v>
+        <v>6614068</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3519,7 +3538,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3529,7 +3548,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,6 +3559,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3556,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120345023</v>
+        <v>120343407</v>
       </c>
       <c r="B27" t="n">
-        <v>91272</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3568,41 +3592,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600529</v>
+        <v>600652</v>
       </c>
       <c r="R27" t="n">
-        <v>6614077</v>
+        <v>6613987</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3631,7 +3660,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3641,7 +3670,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3652,16 +3681,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3678,10 +3697,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120343407</v>
+        <v>120344481</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3694,42 +3713,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600652</v>
+        <v>600773</v>
       </c>
       <c r="R28" t="n">
-        <v>6613987</v>
+        <v>6614013</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3758,7 +3772,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3768,7 +3782,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120342905</v>
+        <v>120344208</v>
       </c>
       <c r="B29" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3807,50 +3821,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600559</v>
+        <v>600749</v>
       </c>
       <c r="R29" t="n">
-        <v>6614068</v>
+        <v>6613964</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3879,7 +3884,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3889,7 +3894,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,11 +3905,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3342,10 +3342,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120344382</v>
+        <v>120344208</v>
       </c>
       <c r="B25" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600771</v>
+        <v>600749</v>
       </c>
       <c r="R25" t="n">
-        <v>6613982</v>
+        <v>6613964</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120342905</v>
+        <v>120343407</v>
       </c>
       <c r="B26" t="n">
-        <v>90600</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3470,31 +3470,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3503,13 +3499,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600559</v>
+        <v>600652</v>
       </c>
       <c r="R26" t="n">
-        <v>6614068</v>
+        <v>6613987</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3538,7 +3534,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3548,7 +3544,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,11 +3555,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3580,10 +3571,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120343407</v>
+        <v>120344481</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3596,42 +3587,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600652</v>
+        <v>600773</v>
       </c>
       <c r="R27" t="n">
-        <v>6613987</v>
+        <v>6614013</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3660,7 +3646,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3670,7 +3656,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,7 +3683,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120344481</v>
+        <v>120342905</v>
       </c>
       <c r="B28" t="n">
         <v>90600</v>
@@ -3730,20 +3716,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600773</v>
+        <v>600559</v>
       </c>
       <c r="R28" t="n">
-        <v>6614013</v>
+        <v>6614068</v>
       </c>
       <c r="S28" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3772,7 +3767,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3782,7 +3777,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3793,6 +3788,11 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120344208</v>
+        <v>120344382</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,25 +3821,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,13 +3849,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600749</v>
+        <v>600771</v>
       </c>
       <c r="R29" t="n">
-        <v>6613964</v>
+        <v>6613982</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3454,10 +3454,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120343407</v>
+        <v>120344481</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3470,42 +3470,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600652</v>
+        <v>600773</v>
       </c>
       <c r="R26" t="n">
-        <v>6613987</v>
+        <v>6614013</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3534,7 +3529,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3544,7 +3539,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3571,10 +3566,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120344481</v>
+        <v>120343407</v>
       </c>
       <c r="B27" t="n">
-        <v>90600</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3587,37 +3582,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600773</v>
+        <v>600652</v>
       </c>
       <c r="R27" t="n">
-        <v>6614013</v>
+        <v>6613987</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3220,10 +3220,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120345023</v>
+        <v>120342905</v>
       </c>
       <c r="B24" t="n">
-        <v>91272</v>
+        <v>90600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,41 +3232,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600529</v>
+        <v>600559</v>
       </c>
       <c r="R24" t="n">
-        <v>6614077</v>
+        <v>6614068</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3295,7 +3304,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3314,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3317,14 +3326,9 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3342,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120344208</v>
+        <v>120345023</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>91272</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,21 +3362,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3382,10 +3386,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600749</v>
+        <v>600529</v>
       </c>
       <c r="R25" t="n">
-        <v>6613964</v>
+        <v>6614077</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3417,7 +3421,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3427,7 +3431,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,6 +3442,16 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3566,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120343407</v>
+        <v>120344382</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>90600</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3582,39 +3596,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600652</v>
+        <v>600771</v>
       </c>
       <c r="R27" t="n">
-        <v>6613987</v>
+        <v>6613982</v>
       </c>
       <c r="S27" t="n">
         <v>8</v>
@@ -3646,7 +3655,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3656,7 +3665,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3683,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120342905</v>
+        <v>120344208</v>
       </c>
       <c r="B28" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,50 +3704,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600559</v>
+        <v>600749</v>
       </c>
       <c r="R28" t="n">
-        <v>6614068</v>
+        <v>6613964</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3788,11 +3788,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3809,53 +3804,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120344382</v>
+        <v>120344691</v>
       </c>
       <c r="B29" t="n">
-        <v>90600</v>
+        <v>94704</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>600771</v>
+        <v>600748</v>
       </c>
       <c r="R29" t="n">
-        <v>6613982</v>
+        <v>6614035</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3884,7 +3888,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3894,7 +3898,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3921,62 +3925,58 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120344691</v>
+        <v>120343407</v>
       </c>
       <c r="B30" t="n">
-        <v>94704</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>600748</v>
+        <v>600652</v>
       </c>
       <c r="R30" t="n">
-        <v>6614035</v>
+        <v>6613987</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3220,10 +3220,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120342905</v>
+        <v>120344208</v>
       </c>
       <c r="B24" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,50 +3232,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600559</v>
+        <v>600749</v>
       </c>
       <c r="R24" t="n">
-        <v>6614068</v>
+        <v>6613964</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3304,7 +3295,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3314,7 +3305,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3325,11 +3316,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3346,10 +3332,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120345023</v>
+        <v>120342905</v>
       </c>
       <c r="B25" t="n">
-        <v>91272</v>
+        <v>90600</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,41 +3344,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600529</v>
+        <v>600559</v>
       </c>
       <c r="R25" t="n">
-        <v>6614077</v>
+        <v>6614068</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3421,7 +3416,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3431,7 +3426,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,14 +3438,9 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3468,10 +3458,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120344481</v>
+        <v>120345023</v>
       </c>
       <c r="B26" t="n">
-        <v>90600</v>
+        <v>91272</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3480,41 +3470,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600773</v>
+        <v>600529</v>
       </c>
       <c r="R26" t="n">
-        <v>6614013</v>
+        <v>6614077</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3543,7 +3533,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3553,7 +3543,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,6 +3554,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3580,7 +3580,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120344382</v>
+        <v>120344481</v>
       </c>
       <c r="B27" t="n">
         <v>90600</v>
@@ -3616,17 +3616,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600771</v>
+        <v>600773</v>
       </c>
       <c r="R27" t="n">
-        <v>6613982</v>
+        <v>6614013</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,10 +3692,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120344208</v>
+        <v>120344382</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3704,25 +3704,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600749</v>
+        <v>600771</v>
       </c>
       <c r="R28" t="n">
-        <v>6613964</v>
+        <v>6613982</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3458,10 +3458,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120345023</v>
+        <v>120344382</v>
       </c>
       <c r="B26" t="n">
-        <v>91272</v>
+        <v>90600</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3470,25 +3470,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3298</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600529</v>
+        <v>600771</v>
       </c>
       <c r="R26" t="n">
-        <v>6614077</v>
+        <v>6613982</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,16 +3554,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3580,10 +3570,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120344481</v>
+        <v>120345023</v>
       </c>
       <c r="B27" t="n">
-        <v>90600</v>
+        <v>91272</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3592,41 +3582,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600773</v>
+        <v>600529</v>
       </c>
       <c r="R27" t="n">
-        <v>6614013</v>
+        <v>6614077</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3655,7 +3645,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3665,7 +3655,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3676,6 +3666,16 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3692,7 +3692,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120344382</v>
+        <v>120344481</v>
       </c>
       <c r="B28" t="n">
         <v>90600</v>
@@ -3728,17 +3728,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600771</v>
+        <v>600773</v>
       </c>
       <c r="R28" t="n">
-        <v>6613982</v>
+        <v>6614013</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -3220,10 +3220,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120344208</v>
+        <v>120342905</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,41 +3232,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600749</v>
+        <v>600559</v>
       </c>
       <c r="R24" t="n">
-        <v>6613964</v>
+        <v>6614068</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3295,7 +3304,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3314,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3316,6 +3325,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3332,7 +3346,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120342905</v>
+        <v>120344382</v>
       </c>
       <c r="B25" t="n">
         <v>90600</v>
@@ -3365,29 +3379,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600559</v>
+        <v>600771</v>
       </c>
       <c r="R25" t="n">
-        <v>6614068</v>
+        <v>6613982</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3416,7 +3421,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3426,7 +3431,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,11 +3442,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3458,10 +3458,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120344382</v>
+        <v>120345023</v>
       </c>
       <c r="B26" t="n">
-        <v>90600</v>
+        <v>91272</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3470,25 +3470,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3498,13 +3498,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600771</v>
+        <v>600529</v>
       </c>
       <c r="R26" t="n">
-        <v>6613982</v>
+        <v>6614077</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,6 +3554,16 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3570,10 +3580,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120345023</v>
+        <v>120344208</v>
       </c>
       <c r="B27" t="n">
-        <v>91272</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3586,21 +3596,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3298</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3610,10 +3620,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600529</v>
+        <v>600749</v>
       </c>
       <c r="R27" t="n">
-        <v>6614077</v>
+        <v>6613964</v>
       </c>
       <c r="S27" t="n">
         <v>6</v>
@@ -3645,7 +3655,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3655,7 +3665,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,16 +3676,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>113242163</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>113242163</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>113242163</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>113242163</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>113242163</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -2432,7 +2432,7 @@
         <v>113242163</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113532120</v>
+        <v>120344208</v>
       </c>
       <c r="B22" t="n">
-        <v>97650</v>
+        <v>91913</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2976,57 +2976,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, S om (mittt) (knärot), Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
         <v>600749</v>
       </c>
       <c r="R22" t="n">
-        <v>6613972</v>
+        <v>6613964</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3048,19 +3032,24 @@
           <t>Björksta</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>U-Väs-1486</t>
-        </is>
-      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3069,33 +3058,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline Haarala</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113532143</v>
+        <v>120345023</v>
       </c>
       <c r="B23" t="n">
-        <v>97650</v>
+        <v>91330</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3104,57 +3088,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600840</v>
+        <v>600529</v>
       </c>
       <c r="R23" t="n">
-        <v>6613984</v>
+        <v>6614077</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3176,19 +3144,24 @@
           <t>Björksta</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>U-Väs-1487</t>
-        </is>
-      </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,33 +3170,38 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline Haarala</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120344208</v>
+        <v>120344481</v>
       </c>
       <c r="B24" t="n">
-        <v>91913</v>
+        <v>90658</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,41 +3210,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600749</v>
+        <v>600773</v>
       </c>
       <c r="R24" t="n">
-        <v>6613964</v>
+        <v>6614013</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3295,7 +3273,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,7 +3283,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,10 +3310,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120345023</v>
+        <v>120344382</v>
       </c>
       <c r="B25" t="n">
-        <v>91330</v>
+        <v>90658</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3344,25 +3322,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3372,13 +3350,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600529</v>
+        <v>600771</v>
       </c>
       <c r="R25" t="n">
-        <v>6614077</v>
+        <v>6613982</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3407,7 +3385,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3417,7 +3395,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3428,16 +3406,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3454,7 +3422,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120344481</v>
+        <v>120342905</v>
       </c>
       <c r="B26" t="n">
         <v>90658</v>
@@ -3487,20 +3455,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600773</v>
+        <v>600559</v>
       </c>
       <c r="R26" t="n">
-        <v>6614013</v>
+        <v>6614068</v>
       </c>
       <c r="S26" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3529,7 +3506,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3539,7 +3516,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,6 +3527,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3566,53 +3548,62 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120344382</v>
+        <v>120344691</v>
       </c>
       <c r="B27" t="n">
-        <v>90658</v>
+        <v>94781</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600771</v>
+        <v>600748</v>
       </c>
       <c r="R27" t="n">
-        <v>6613982</v>
+        <v>6614035</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3641,7 +3632,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3651,7 +3642,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3678,14 +3669,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120342905</v>
+        <v>120343407</v>
       </c>
       <c r="B28" t="n">
-        <v>90658</v>
+        <v>57363</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3694,31 +3685,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3727,13 +3714,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600559</v>
+        <v>600652</v>
       </c>
       <c r="R28" t="n">
-        <v>6614068</v>
+        <v>6613987</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3762,7 +3749,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3772,7 +3759,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,11 +3770,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3801,244 +3783,6 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>120344691</v>
-      </c>
-      <c r="B29" t="n">
-        <v>94781</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>2180</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Blåmossa</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Leucobryum glaucum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Skansen, Skansen, Vstm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>600748</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6614035</v>
-      </c>
-      <c r="S29" t="n">
-        <v>12</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Västerås</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Björksta</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>120343407</v>
-      </c>
-      <c r="B30" t="n">
-        <v>57363</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>600652</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6613987</v>
-      </c>
-      <c r="S30" t="n">
-        <v>8</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Västerås</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Björksta</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110282848</v>
+        <v>113242085</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>789</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Raggtaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum mirabile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600839.9318167433</v>
+        <v>600656</v>
       </c>
       <c r="R2" t="n">
-        <v>6613983.990819811</v>
+        <v>6613968</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110282828</v>
+        <v>110282835</v>
       </c>
       <c r="B3" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,31 +787,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -854,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600787.8656294679</v>
+        <v>600805</v>
       </c>
       <c r="R3" t="n">
-        <v>6613904.709995793</v>
+        <v>6613969</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,28 +855,17 @@
           <t>2023-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -927,66 +884,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110282764</v>
+        <v>113241998</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600749.0751519018</v>
+        <v>600553</v>
       </c>
       <c r="R4" t="n">
-        <v>6613971.934424319</v>
+        <v>6614072</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,22 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,34 +963,37 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110282846</v>
+        <v>113242256</v>
       </c>
       <c r="B5" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,50 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600839.9318167433</v>
+        <v>600764</v>
       </c>
       <c r="R5" t="n">
-        <v>6613983.990819811</v>
+        <v>6614027</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1142,22 +1055,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,27 +1075,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110282836</v>
+        <v>120344691</v>
       </c>
       <c r="B6" t="n">
-        <v>89793</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,48 +1102,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4217</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600805.3583702671</v>
+        <v>600748</v>
       </c>
       <c r="R6" t="n">
-        <v>6613969.910894822</v>
+        <v>6614035</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1265,22 +1165,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,76 +1195,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110282820</v>
+        <v>120345023</v>
       </c>
       <c r="B7" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600724.7123983201</v>
+        <v>600529</v>
       </c>
       <c r="R7" t="n">
-        <v>6614086.574870056</v>
+        <v>6614077</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1388,104 +1272,97 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110282835</v>
+        <v>113242035</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>3518</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600805.3583702671</v>
+        <v>600760</v>
       </c>
       <c r="R8" t="n">
-        <v>6613969.910894822</v>
+        <v>6614032</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1512,22 +1389,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,27 +1409,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110282856</v>
+        <v>110282836</v>
       </c>
       <c r="B9" t="n">
-        <v>89802</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,21 +1436,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1594,7 +1460,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1605,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600677.6983460309</v>
+        <v>600805</v>
       </c>
       <c r="R9" t="n">
-        <v>6613951.301940188</v>
+        <v>6613969</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1638,19 +1504,9 @@
           <t>2023-06-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,15 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242126</v>
+        <v>113242125</v>
       </c>
       <c r="B10" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600639</v>
+        <v>600694</v>
       </c>
       <c r="R10" t="n">
-        <v>6613970</v>
+        <v>6613968</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1783,15 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242125</v>
+        <v>113242126</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600694</v>
+        <v>600639</v>
       </c>
       <c r="R11" t="n">
-        <v>6613968</v>
+        <v>6613970</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1889,37 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242240</v>
+        <v>113242233</v>
       </c>
       <c r="B12" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1929,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600690</v>
+        <v>600782</v>
       </c>
       <c r="R12" t="n">
-        <v>6614074</v>
+        <v>6613922</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1975,11 +1816,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>granved</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2000,15 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113241998</v>
+        <v>113242234</v>
       </c>
       <c r="B13" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2016,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2040,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600553</v>
+        <v>600684</v>
       </c>
       <c r="R13" t="n">
-        <v>6614072</v>
+        <v>6613957</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2086,11 +1917,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2111,53 +1937,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113242035</v>
+        <v>120344208</v>
       </c>
       <c r="B14" t="n">
-        <v>84122</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3518</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600760</v>
+        <v>600749</v>
       </c>
       <c r="R14" t="n">
-        <v>6614032</v>
+        <v>6613964</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2181,19 +2002,29 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2201,31 +2032,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113242234</v>
+        <v>110282856</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2233,34 +2055,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600684</v>
+        <v>600678</v>
       </c>
       <c r="R15" t="n">
-        <v>6613957</v>
+        <v>6613951</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2287,12 +2120,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,31 +2140,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242233</v>
+        <v>113242201</v>
       </c>
       <c r="B16" t="n">
-        <v>91605</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,21 +2163,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2363,10 +2187,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600782</v>
+        <v>600760</v>
       </c>
       <c r="R16" t="n">
-        <v>6613922</v>
+        <v>6614099</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2429,50 +2253,56 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113242163</v>
+        <v>110282820</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600840</v>
+        <v>600725</v>
       </c>
       <c r="R17" t="n">
-        <v>6614040</v>
+        <v>6614087</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2499,12 +2329,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,72 +2343,75 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113242256</v>
+        <v>110282828</v>
       </c>
       <c r="B18" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600764</v>
+        <v>600788</v>
       </c>
       <c r="R18" t="n">
-        <v>6614027</v>
+        <v>6613905</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2605,12 +2438,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,75 +2452,76 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113241936</v>
+        <v>120342905</v>
       </c>
       <c r="B19" t="n">
-        <v>90297</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600702</v>
+        <v>600559</v>
       </c>
       <c r="R19" t="n">
-        <v>6614016</v>
+        <v>6614068</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2711,12 +2545,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,77 +2572,68 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113242085</v>
+        <v>120344382</v>
       </c>
       <c r="B20" t="n">
-        <v>91615</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>789</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raggtaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum mirabile</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600656</v>
+        <v>600771</v>
       </c>
       <c r="R20" t="n">
-        <v>6613968</v>
+        <v>6613982</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2822,12 +2657,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2842,69 +2687,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113242201</v>
+        <v>120344481</v>
       </c>
       <c r="B21" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600760</v>
+        <v>600773</v>
       </c>
       <c r="R21" t="n">
-        <v>6614099</v>
+        <v>6614013</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2928,12 +2764,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,31 +2794,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120344208</v>
+        <v>113241936</v>
       </c>
       <c r="B22" t="n">
-        <v>91913</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,37 +2817,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600749</v>
+        <v>600702</v>
       </c>
       <c r="R22" t="n">
-        <v>6613964</v>
+        <v>6614016</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3034,57 +2871,51 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120345023</v>
+        <v>120343407</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3092,37 +2923,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600529</v>
+        <v>600652</v>
       </c>
       <c r="R23" t="n">
-        <v>6614077</v>
+        <v>6613987</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3151,7 +2987,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,27 +2997,17 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3198,53 +3024,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120344481</v>
+        <v>113242240</v>
       </c>
       <c r="B24" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600773</v>
+        <v>600690</v>
       </c>
       <c r="R24" t="n">
-        <v>6614013</v>
+        <v>6614074</v>
       </c>
       <c r="S24" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3268,22 +3089,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3294,69 +3105,89 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120344382</v>
+        <v>110282764</v>
       </c>
       <c r="B25" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600771</v>
+        <v>600749</v>
       </c>
       <c r="R25" t="n">
-        <v>6613982</v>
+        <v>6613972</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3380,22 +3211,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:40</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:40</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3404,80 +3225,83 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120342905</v>
+        <v>110282848</v>
       </c>
       <c r="B26" t="n">
-        <v>90658</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600559</v>
+        <v>600840</v>
       </c>
       <c r="R26" t="n">
-        <v>6614068</v>
+        <v>6613985</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3501,22 +3325,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,83 +3341,64 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120344691</v>
+        <v>113242163</v>
       </c>
       <c r="B27" t="n">
-        <v>94781</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600748</v>
+        <v>600840</v>
       </c>
       <c r="R27" t="n">
-        <v>6614035</v>
+        <v>6614040</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3627,22 +3422,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3657,70 +3442,80 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120343407</v>
+        <v>113532143</v>
       </c>
       <c r="B28" t="n">
-        <v>57363</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600652</v>
+        <v>600840</v>
       </c>
       <c r="R28" t="n">
-        <v>6613987</v>
+        <v>6613984</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3742,24 +3537,19 @@
           <t>Björksta</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>U-Väs-1487</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,21 +3558,139 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Bo Eriksson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Jacob Rudhe, Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>110282846</v>
+      </c>
+      <c r="B29" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>S Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>600840</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6613985</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,48 +990,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113242256</v>
+        <v>135158816</v>
       </c>
       <c r="B5" t="n">
-        <v>96708</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>Skansen S, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600764</v>
+        <v>600652</v>
       </c>
       <c r="R5" t="n">
-        <v>6614027</v>
+        <v>6613977</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1055,12 +1060,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,27 +1076,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120344691</v>
+        <v>113242256</v>
       </c>
       <c r="B6" t="n">
         <v>96708</v>
@@ -1119,29 +1128,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600748</v>
+        <v>600764</v>
       </c>
       <c r="R6" t="n">
-        <v>6614035</v>
+        <v>6614027</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,22 +1165,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,22 +1185,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120345023</v>
+        <v>120344691</v>
       </c>
       <c r="B7" t="n">
-        <v>92632</v>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1218,37 +1212,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3298</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600529</v>
+        <v>600748</v>
       </c>
       <c r="R7" t="n">
-        <v>6614077</v>
+        <v>6614035</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1277,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1287,27 +1290,17 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Död ved  vedartad växt</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Dead wood</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1324,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113242035</v>
+        <v>120345023</v>
       </c>
       <c r="B8" t="n">
-        <v>85274</v>
+        <v>92632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,37 +1328,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3518</v>
+        <v>3298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600760</v>
+        <v>600529</v>
       </c>
       <c r="R8" t="n">
-        <v>6614032</v>
+        <v>6614077</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,46 +1382,62 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död ved  vedartad växt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead wood</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110282836</v>
+        <v>113242035</v>
       </c>
       <c r="B9" t="n">
-        <v>92333</v>
+        <v>85274</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1436,45 +1445,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>3518</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600805</v>
+        <v>600760</v>
       </c>
       <c r="R9" t="n">
-        <v>6613969</v>
+        <v>6614032</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1501,12 +1499,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,57 +1519,72 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113242125</v>
+        <v>110282836</v>
       </c>
       <c r="B10" t="n">
-        <v>93189</v>
+        <v>92333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600694</v>
+        <v>600805</v>
       </c>
       <c r="R10" t="n">
-        <v>6613968</v>
+        <v>6613969</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1598,12 +1611,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,23 +1631,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113242126</v>
+        <v>113242125</v>
       </c>
       <c r="B11" t="n">
         <v>93189</v>
@@ -1669,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600639</v>
+        <v>600694</v>
       </c>
       <c r="R11" t="n">
-        <v>6613970</v>
+        <v>6613968</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1735,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113242233</v>
+        <v>113242126</v>
       </c>
       <c r="B12" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600782</v>
+        <v>600639</v>
       </c>
       <c r="R12" t="n">
-        <v>6613922</v>
+        <v>6613970</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1836,7 +1845,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113242234</v>
+        <v>113242233</v>
       </c>
       <c r="B13" t="n">
         <v>93197</v>
@@ -1871,10 +1880,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600684</v>
+        <v>600782</v>
       </c>
       <c r="R13" t="n">
-        <v>6613957</v>
+        <v>6613922</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1937,7 +1946,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120344208</v>
+        <v>113242234</v>
       </c>
       <c r="B14" t="n">
         <v>93197</v>
@@ -1968,17 +1977,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600749</v>
+        <v>600684</v>
       </c>
       <c r="R14" t="n">
-        <v>6613964</v>
+        <v>6613957</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2002,29 +2011,19 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2032,71 +2031,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110282856</v>
+        <v>120344208</v>
       </c>
       <c r="B15" t="n">
-        <v>92348</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600678</v>
+        <v>600749</v>
       </c>
       <c r="R15" t="n">
-        <v>6613951</v>
+        <v>6613964</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2120,19 +2112,29 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2140,19 +2142,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113242201</v>
+        <v>110282856</v>
       </c>
       <c r="B16" t="n">
         <v>92348</v>
@@ -2180,17 +2182,28 @@
           <t>(Fr.) Pat.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>600760</v>
+        <v>600678</v>
       </c>
       <c r="R16" t="n">
-        <v>6614099</v>
+        <v>6613951</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2217,12 +2230,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,72 +2250,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110282820</v>
+        <v>113242201</v>
       </c>
       <c r="B17" t="n">
-        <v>91930</v>
+        <v>92348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>600725</v>
+        <v>600760</v>
       </c>
       <c r="R17" t="n">
-        <v>6614087</v>
+        <v>6614099</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2329,12 +2327,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,26 +2341,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110282828</v>
+        <v>110282820</v>
       </c>
       <c r="B18" t="n">
         <v>91930</v>
@@ -2392,7 +2393,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2408,10 +2409,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>600788</v>
+        <v>600725</v>
       </c>
       <c r="R18" t="n">
-        <v>6613905</v>
+        <v>6614087</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2471,7 +2472,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120342905</v>
+        <v>110282828</v>
       </c>
       <c r="B19" t="n">
         <v>91930</v>
@@ -2501,7 +2502,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2509,19 +2510,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>600559</v>
+        <v>600788</v>
       </c>
       <c r="R19" t="n">
-        <v>6614068</v>
+        <v>6613905</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2545,22 +2548,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,30 +2562,26 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120344382</v>
+        <v>120342905</v>
       </c>
       <c r="B20" t="n">
         <v>91930</v>
@@ -2620,20 +2609,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>600771</v>
+        <v>600559</v>
       </c>
       <c r="R20" t="n">
-        <v>6613982</v>
+        <v>6614068</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2662,7 +2660,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2672,7 +2670,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2683,6 +2681,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2699,7 +2702,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120344481</v>
+        <v>120344382</v>
       </c>
       <c r="B21" t="n">
         <v>91930</v>
@@ -2730,17 +2733,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skansen, Skansen, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>600773</v>
+        <v>600771</v>
       </c>
       <c r="R21" t="n">
-        <v>6614013</v>
+        <v>6613982</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2769,7 +2772,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2779,7 +2782,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2806,48 +2809,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113241936</v>
+        <v>120344481</v>
       </c>
       <c r="B22" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>Skansen, Skansen, Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>600702</v>
+        <v>600773</v>
       </c>
       <c r="R22" t="n">
-        <v>6614016</v>
+        <v>6614013</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2871,12 +2874,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2887,78 +2900,69 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120343407</v>
+        <v>135158817</v>
       </c>
       <c r="B23" t="n">
-        <v>57950</v>
+        <v>91995</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>S Frögärde, S Frögärde, Vstm</t>
+          <t>Skansen S, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>600652</v>
+        <v>600801</v>
       </c>
       <c r="R23" t="n">
-        <v>6613987</v>
+        <v>6613905</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2982,22 +2986,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3008,64 +3002,77 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lars Bohlin</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113242240</v>
+        <v>135158818</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>91995</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Frögärde, Vstm</t>
+          <t>Skansen S, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>600690</v>
+        <v>600798</v>
       </c>
       <c r="R24" t="n">
-        <v>6614074</v>
+        <v>6613915</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3089,12 +3096,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3106,85 +3113,68 @@
       <c r="AG24" t="b">
         <v>0</v>
       </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>granved</t>
+          <t>1 substratenheter</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Markus Rehnberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
-        </is>
-      </c>
+          <t>Markus Rehnberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110282764</v>
+        <v>113241936</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>600749</v>
+        <v>600702</v>
       </c>
       <c r="R25" t="n">
-        <v>6613972</v>
+        <v>6614016</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3211,12 +3201,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,83 +3215,80 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110282848</v>
+        <v>120343407</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>S Frögärde, Vstm</t>
+          <t>S Frögärde, S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>600840</v>
+        <v>600652</v>
       </c>
       <c r="R26" t="n">
-        <v>6613985</v>
+        <v>6613987</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3325,12 +3312,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,44 +3342,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline  Haarala</t>
+          <t>Lars Bohlin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>113242163</v>
+        <v>113242240</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3392,10 +3389,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>600840</v>
+        <v>600690</v>
       </c>
       <c r="R27" t="n">
-        <v>6614040</v>
+        <v>6614074</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3438,6 +3435,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>granved</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3458,7 +3460,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>113532143</v>
+        <v>110282764</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3488,7 +3490,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3505,14 +3507,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+          <t>S Frögärde, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>600840</v>
+        <v>600749</v>
       </c>
       <c r="R28" t="n">
-        <v>6613984</v>
+        <v>6613972</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3537,11 +3539,6 @@
           <t>Björksta</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>U-Väs-1487</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
           <t>2023-06-19</t>
@@ -3565,53 +3562,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo Eriksson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Caroline Haarala</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110282846</v>
+        <v>110282848</v>
       </c>
       <c r="B29" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3621,7 +3614,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -3691,6 +3684,343 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>113242163</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>600840</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6614040</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-11-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Värdefulla skogsmiljöer i Västmanlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>113532143</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Frögärde, S om (NO) (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>600840</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6613984</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>U-Väs-1487</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe, Caroline Haarala</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>110282846</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>S Frögärde, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>600840</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6613985</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe, Caroline  Haarala</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242085</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113241998</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158816</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242256</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120344691</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120345023</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242035</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282836</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242125</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242126</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242233</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2044,6 +2109,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242234</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2151,6 +2221,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120344208</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2259,6 +2334,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282856</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2360,6 +2440,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242201</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2554,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282820</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2578,6 +2668,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282828</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2699,6 +2794,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120342905</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2806,6 +2906,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120344382</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2913,6 +3018,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120344481</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3023,6 +3133,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158817</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158818</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3239,6 +3359,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113241936</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3351,6 +3476,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120343407</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3457,6 +3587,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242240</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3571,6 +3706,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282764</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3684,6 +3824,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282848</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3785,6 +3930,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113242163</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3908,6 +4058,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113532143</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4021,8 +4176,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110282846</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>135158816</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>135158817</v>
       </c>
       <c r="B23" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>135158818</v>
       </c>
       <c r="B24" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 52775-2022 artfynd.xlsx
+++ b/artfynd/A 52775-2022 artfynd.xlsx
@@ -1013,7 +1013,7 @@
         <v>135158816</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>135158817</v>
       </c>
       <c r="B23" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>135158818</v>
       </c>
       <c r="B24" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
